--- a/新数据生成/关卡表/10050.xlsx
+++ b/新数据生成/关卡表/10050.xlsx
@@ -459,8 +459,8 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="13.2" customWidth="1" min="13" max="13"/>
     <col width="13.2" customWidth="1" min="14" max="14"/>
-    <col width="17.6" customWidth="1" min="15" max="15"/>
-    <col width="4.4" customWidth="1" min="16" max="16"/>
+    <col width="13.2" customWidth="1" min="15" max="15"/>
+    <col width="13.2" customWidth="1" min="16" max="16"/>
     <col width="4.4" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -693,10 +693,14 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>角色平均等级</t>
-        </is>
-      </c>
-      <c r="P6" s="1" t="n"/>
+          <t>阵容强度</t>
+        </is>
+      </c>
+      <c r="P6" s="1" t="inlineStr">
+        <is>
+          <t>参考等级</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="n">
@@ -709,30 +713,30 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>16.3</v>
+        <v>18</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-9.5</v>
+        <v>-3.5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -741,7 +745,10 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -752,23 +759,23 @@
         <v>2008</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>16.3</v>
+        <v>18</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-9.5</v>
+        <v>-3.5</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -781,7 +788,10 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -789,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="n">
@@ -805,14 +815,14 @@
         <v>1.2</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>16.3</v>
+        <v>18</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-9.5</v>
+        <v>-3.5</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -821,7 +831,10 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -832,10 +845,10 @@
         <v>2002</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="n">
@@ -845,10 +858,10 @@
         <v>1.1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>18</v>
+        <v>24.3</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -861,7 +874,10 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -869,30 +885,30 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>18</v>
+        <v>24.3</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>刘易斯</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -901,47 +917,37 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="n">
-        <v>18</v>
+        <v>24.3</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>垃圾刺客</t>
-        </is>
-      </c>
+        <v>5.9</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>5</v>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -955,20 +961,20 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>11.3</v>
+        <v>8</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-2.5</v>
+        <v>0.9</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
@@ -981,7 +987,10 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -989,30 +998,30 @@
         <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>11.3</v>
+        <v>8</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-2.5</v>
+        <v>0.9</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1021,47 +1030,37 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="D15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="n">
-        <v>11.3</v>
+        <v>8</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O15" s="2" t="n">
-        <v>5</v>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1069,39 +1068,42 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-6.8</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>萨哈比精英坦克</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1109,13 +1111,13 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="n">
@@ -1125,49 +1127,69 @@
         <v>1.1</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>-6.8</v>
+        <v>6</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>精射手</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="D18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K18" s="2" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>刘易斯</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O18" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1181,20 +1203,20 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>18.6</v>
+        <v>10.5</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>6</v>
+        <v>-7.1</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1203,11 +1225,14 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1218,23 +1243,23 @@
         <v>2003</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>18.6</v>
+        <v>10.5</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6</v>
+        <v>-7.1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1243,51 +1268,61 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="D21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>2008</v>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3998</t>
+        </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>39564</v>
+      </c>
       <c r="I21" s="2" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>18.6</v>
+        <v>10.5</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>6</v>
+        <v>-7.1</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>技能Boss2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1298,23 +1333,23 @@
         <v>2002</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>19.3</v>
+        <v>22</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1327,7 +1362,10 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1338,23 +1376,23 @@
         <v>2007</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>19.3</v>
+        <v>22</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -1367,7 +1405,10 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1375,30 +1416,30 @@
         <v>6</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>19.3</v>
+        <v>22</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>精射手</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -1407,7 +1448,10 @@
         </is>
       </c>
       <c r="O24" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1415,30 +1459,30 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>22</v>
+        <v>14.1</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>-7.2</v>
+        <v>-6.2</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -1447,7 +1491,10 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1458,10 +1505,10 @@
         <v>2004</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
@@ -1471,10 +1518,10 @@
         <v>1.1</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>22</v>
+        <v>14.1</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>-7.2</v>
+        <v>-6.2</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -1487,7 +1534,10 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1501,10 +1551,10 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="n">
-        <v>22</v>
+        <v>14.1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>-7.2</v>
+        <v>-6.2</v>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
@@ -1512,8 +1562,9 @@
           <t>轻松</t>
         </is>
       </c>
-      <c r="O27" s="2" t="n">
-        <v>5</v>
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -1531,16 +1582,16 @@
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J28" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="J28" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K28" s="2" t="n">
-        <v>11.3</v>
+        <v>8.5</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1.6</v>
+        <v>-1.6</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
@@ -1553,7 +1604,10 @@
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1564,23 +1618,23 @@
         <v>2004</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>11.3</v>
+        <v>8.5</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>1.6</v>
+        <v>-1.6</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -1593,47 +1647,37 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="n">
-        <v>11.3</v>
+        <v>8.5</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>-1.6</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O30" s="2" t="n">
-        <v>5</v>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1644,10 +1688,10 @@
         <v>2002</v>
       </c>
       <c r="F31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="2" t="n">
         <v>3</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>4</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
@@ -1657,10 +1701,10 @@
         <v>1.1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -1673,7 +1717,10 @@
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1681,30 +1728,30 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>垃圾刺客</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -1713,33 +1760,53 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
-      <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="n">
+        <v>2005</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K33" s="2" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>刘易斯</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
       <c r="O33" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1747,109 +1814,128 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>13.3</v>
+        <v>17.7</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>-3.5</v>
+        <v>8.1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="D35" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>3998</t>
-        </is>
+      <c r="E35" s="2" t="n">
+        <v>2008</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>77274</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>13.3</v>
+        <v>17.7</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>-3.5</v>
+        <v>8.1</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>技能Boss2</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="D36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="n">
+        <v>2004</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="inlineStr"/>
-      <c r="J36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" s="2" t="n">
-        <v>13.3</v>
+        <v>17.7</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+        <v>8.1</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>残酷射手</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O36" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1857,30 +1943,30 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>11.3</v>
+        <v>13.1</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>-2.1</v>
+        <v>-4.4</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -1889,7 +1975,10 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1897,30 +1986,30 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>11.3</v>
+        <v>13.1</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>-2.1</v>
+        <v>-4.4</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -1929,33 +2018,53 @@
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="D39" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K39" s="2" t="n">
-        <v>11.3</v>
+        <v>13.1</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+        <v>-4.4</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>影流之主</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
       <c r="O39" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1969,20 +2078,20 @@
         <v>2</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>21.7</v>
+        <v>17</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -1995,7 +2104,10 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2003,30 +2115,30 @@
         <v>12</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>21.7</v>
+        <v>17</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>精射手</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -2035,7 +2147,10 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2043,30 +2158,30 @@
         <v>12</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>21.7</v>
+        <v>17</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>垃圾刺客</t>
+          <t>刘易斯</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -2075,7 +2190,10 @@
         </is>
       </c>
       <c r="O42" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2083,39 +2201,42 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>20.7</v>
+        <v>13.8</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-3.6</v>
+        <v>2.6</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2123,79 +2244,69 @@
         <v>13</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>20.7</v>
+        <v>13.8</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>-3.6</v>
+        <v>2.6</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="D45" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="n">
-        <v>20.7</v>
+        <v>13.8</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>5</v>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2203,39 +2314,42 @@
         <v>14</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>9</v>
+        <v>17.1</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2243,65 +2357,85 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>9</v>
+        <v>17.1</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>2.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="D48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K48" s="2" t="n">
-        <v>9</v>
+        <v>17.1</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>影流之主</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O48" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -2312,23 +2446,23 @@
         <v>2001</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>27.1</v>
+        <v>29.5</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>6.6</v>
+        <v>-0.5</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -2337,53 +2471,61 @@
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="D50" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>3003</v>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>3999</t>
+        </is>
       </c>
       <c r="F50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>8460.4</v>
+        <v>39564</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>27.1</v>
+        <v>29.5</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>6.6</v>
+        <v>-0.5</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>技能Boss1</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2397,19 +2539,20 @@
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="n">
-        <v>27.1</v>
+        <v>29.5</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>6.6</v>
+        <v>-0.5</v>
       </c>
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>5</v>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -2417,39 +2560,42 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>22.3</v>
+        <v>8.6</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>-8.4</v>
+        <v>0.8</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2457,65 +2603,85 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>22.3</v>
+        <v>8.6</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>-8.4</v>
+        <v>0.8</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="D54" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K54" s="2" t="n">
-        <v>22.3</v>
+        <v>8.6</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>-8.4</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>影流之主</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O54" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -2526,23 +2692,23 @@
         <v>2002</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
@@ -2555,7 +2721,10 @@
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2563,30 +2732,30 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>刘易斯</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -2595,33 +2764,53 @@
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="D57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="n">
+        <v>2007</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K57" s="2" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+        <v>2.9</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>垃圾刺客</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
       <c r="O57" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2629,30 +2818,30 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>10.1</v>
+        <v>14.9</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>-0.9</v>
+        <v>2.3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>残酷射手</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -2661,7 +2850,10 @@
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2669,30 +2861,30 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>10.1</v>
+        <v>14.9</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>-0.9</v>
+        <v>2.3</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>影流之主</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -2701,7 +2893,10 @@
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2715,10 +2910,10 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="n">
-        <v>10.1</v>
+        <v>14.9</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>-0.9</v>
+        <v>2.3</v>
       </c>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
@@ -2726,8 +2921,9 @@
           <t>一般</t>
         </is>
       </c>
-      <c r="O60" s="2" t="n">
-        <v>5</v>
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2735,7 +2931,7 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>1</v>
@@ -2745,29 +2941,32 @@
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>19.2</v>
+        <v>10.6</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>2.8</v>
+        <v>-0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2775,79 +2974,69 @@
         <v>19</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="F62" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G62" s="2" t="n">
         <v>5</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>10</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>19.2</v>
+        <v>10.6</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>2.8</v>
+        <v>-0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>泰森</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="D63" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="n">
-        <v>19.2</v>
+        <v>10.6</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>精射手</t>
-        </is>
-      </c>
+        <v>-0</v>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="n">
-        <v>5</v>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2855,39 +3044,42 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2008</v>
+        <v>2001</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>6.4</v>
+        <v>20.8</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>普通坦克</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2898,23 +3090,23 @@
         <v>2003</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>6.4</v>
+        <v>20.8</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -2923,11 +3115,14 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2941,19 +3136,20 @@
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="n">
-        <v>6.4</v>
+        <v>20.8</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="n">
-        <v>5</v>
+          <t>地狱</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/新数据生成/关卡表/10050.xlsx
+++ b/新数据生成/关卡表/10050.xlsx
@@ -713,30 +713,30 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2003</v>
+        <v>2064</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>24</v>
+        <v>21.5</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-3.5</v>
+        <v>-9.9</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -756,10 +756,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2008</v>
+        <v>2066</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>1</v>
@@ -769,17 +769,17 @@
         <v>0.7</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>24</v>
+        <v>21.5</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>-3.5</v>
+        <v>-9.9</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -788,10 +788,10 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -799,30 +799,30 @@
         <v>1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2004</v>
+        <v>2079</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>24</v>
+        <v>21.5</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>-3.5</v>
+        <v>-9.9</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>冬犀牛</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -842,10 +842,10 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2002</v>
+        <v>2083</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>1</v>
@@ -858,14 +858,14 @@
         <v>1.1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>精英冬龟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -874,10 +874,10 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -885,30 +885,30 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2005</v>
+        <v>2081</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>精英冬雪人</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -934,10 +934,10 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -955,30 +955,30 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2003</v>
+        <v>2065</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>10.9</v>
+        <v>8.1</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-0.9</v>
+        <v>-4.1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>双头兽人</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -998,30 +998,30 @@
         <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2008</v>
+        <v>2066</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>10.9</v>
+        <v>8.1</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>-0.9</v>
+        <v>-4.1</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="O14" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1041,30 +1041,30 @@
         <v>3</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2004</v>
+        <v>2064</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>10.9</v>
+        <v>8.1</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>-0.9</v>
+        <v>-4.1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1073,10 +1073,10 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1084,30 +1084,30 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2002</v>
+        <v>2082</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>23.9</v>
+        <v>21.2</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>精英冬石怪</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1116,10 +1116,10 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1127,30 +1127,30 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2006</v>
+        <v>2081</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>23.9</v>
+        <v>21.2</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>精英冬雪人</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1176,10 +1176,10 @@
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="n">
-        <v>23.9</v>
+        <v>21.2</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1197,58 +1197,62 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2001</v>
+        <v>2062</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>17.4</v>
+        <v>26.9</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>7.6</v>
+        <v>-7.3</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="D20" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>2008</v>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3904</t>
+        </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="n">
+        <v>9450</v>
+      </c>
       <c r="I20" s="2" t="n">
         <v>1</v>
       </c>
@@ -1256,69 +1260,53 @@
         <v>1.2</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>17.4</v>
+        <v>26.9</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>7.6</v>
+        <v>-7.3</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>诅咒恶鬼</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="D21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>2004</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="n">
-        <v>17.4</v>
+        <v>26.9</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>残酷射手</t>
-        </is>
-      </c>
+        <v>-7.3</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>3.7</v>
-      </c>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1326,42 +1314,42 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2002</v>
+        <v>2079</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>22.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>4</v>
+        <v>-0.9</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>冬犀牛</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1369,69 +1357,85 @@
         <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2006</v>
+        <v>2074</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>22.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>4</v>
+        <v>-0.9</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>冬蝾螈</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="D24" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="n">
+        <v>2064</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K24" s="2" t="n">
-        <v>22.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+        <v>-0.9</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>红蘑菇</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P24" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1439,42 +1443,42 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2004</v>
+        <v>2070</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>17.7</v>
+        <v>13.5</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>-4</v>
+        <v>3.4</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>精英绿龟</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1482,42 +1486,42 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2008</v>
+        <v>2085</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>17.7</v>
+        <v>13.5</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>-4</v>
+        <v>3.4</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>精英冬犀牛</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1525,42 +1529,42 @@
         <v>7</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2003</v>
+        <v>2072</v>
       </c>
       <c r="F27" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G27" s="2" t="n">
         <v>8</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>2</v>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>17.7</v>
+        <v>13.5</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>-4</v>
+        <v>3.4</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>精英双头兽人</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1568,42 +1572,42 @@
         <v>8</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2001</v>
+        <v>2060</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>12.2</v>
+        <v>21.2</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>-4.1</v>
+        <v>-5</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>蓝雪人</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O28" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -1611,69 +1615,85 @@
         <v>8</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>2004</v>
+        <v>2064</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>12.2</v>
+        <v>21.2</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>-4.1</v>
+        <v>-5</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="D30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K30" s="2" t="n">
-        <v>12.2</v>
+        <v>21.2</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>冬雪人</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr"/>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P30" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1681,42 +1701,42 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2002</v>
+        <v>2077</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>17.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>8.9</v>
+        <v>-4.5</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>冬龟</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1724,85 +1744,69 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2006</v>
+        <v>2064</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>17.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>8.9</v>
+        <v>-4.5</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="D33" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="n">
-        <v>17.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>垃圾刺客</t>
-        </is>
-      </c>
+        <v>-4.5</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v>3.7</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
       <c r="P33" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -1810,42 +1814,42 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2001</v>
+        <v>2063</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>12.6</v>
+        <v>16.4</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>-2.4</v>
+        <v>4.5</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>绿龟</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -1853,89 +1857,85 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2004</v>
+        <v>2079</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>12.6</v>
+        <v>16.4</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>-2.4</v>
+        <v>4.5</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>冬犀牛</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O35" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P35" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="D36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>3998</t>
-        </is>
+      <c r="E36" s="2" t="n">
+        <v>2064</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>39564</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>12.6</v>
+        <v>16.4</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>-2.4</v>
+        <v>4.5</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>技能Boss2</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O36" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P36" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -1943,42 +1943,42 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2002</v>
+        <v>2074</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2.5</v>
+        <v>-7.1</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>冬蝾螈</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P37" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -1986,85 +1986,69 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2005</v>
+        <v>2064</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
         <v>0.7</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>2.5</v>
+        <v>-7.1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>刘易斯</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O38" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P38" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="D39" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>精射手</t>
-        </is>
-      </c>
+        <v>-7.1</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="n">
-        <v>3.7</v>
-      </c>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2072,30 +2056,30 @@
         <v>12</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2003</v>
+        <v>2061</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>13.3</v>
+        <v>6.2</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>-1.2</v>
+        <v>-1.7</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>蓝胖子</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -2104,10 +2088,10 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P40" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2115,30 +2099,30 @@
         <v>12</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2004</v>
+        <v>2079</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J41" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="J41" s="2" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K41" s="2" t="n">
-        <v>13.3</v>
+        <v>6.2</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>-1.2</v>
+        <v>-1.7</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>冬犀牛</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -2147,10 +2131,10 @@
         </is>
       </c>
       <c r="O41" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P41" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -2158,30 +2142,30 @@
         <v>12</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>2008</v>
+        <v>2065</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>13.3</v>
+        <v>6.2</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>-1.2</v>
+        <v>-1.7</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>双头兽人</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -2190,10 +2174,10 @@
         </is>
       </c>
       <c r="O42" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2201,42 +2185,42 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2002</v>
+        <v>2079</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>20.7</v>
+        <v>29.4</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>6.1</v>
+        <v>-4.8</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>冬犀牛</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O43" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P43" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -2244,85 +2228,69 @@
         <v>13</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2006</v>
+        <v>2060</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>20.7</v>
+        <v>29.4</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>6.1</v>
+        <v>-4.8</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>蓝雪人</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O44" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P44" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="D45" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>2007</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G45" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="n">
-        <v>20.7</v>
+        <v>29.4</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>垃圾刺客</t>
-        </is>
-      </c>
+        <v>-4.8</v>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="n">
-        <v>3.7</v>
-      </c>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -2330,42 +2298,42 @@
         <v>14</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2003</v>
+        <v>2069</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>14.1</v>
+        <v>20.6</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>-6</v>
+        <v>3.4</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>精英蓝兔子</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P46" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -2373,85 +2341,69 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2004</v>
+        <v>2085</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>14.1</v>
+        <v>20.6</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>-6</v>
+        <v>3.4</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>残酷射手</t>
+          <t>精英冬犀牛</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P47" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="D48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>3</v>
-      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="n">
-        <v>14.1</v>
+        <v>20.6</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>3.4</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>3.7</v>
-      </c>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -2459,116 +2411,128 @@
         <v>15</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2001</v>
+        <v>2062</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>26.3</v>
+        <v>11</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P49" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="D50" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>3998</t>
-        </is>
+      <c r="E50" s="2" t="n">
+        <v>2066</v>
       </c>
       <c r="F50" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" s="2" t="n">
-        <v>39564</v>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K50" s="2" t="n">
-        <v>26.3</v>
+        <v>11</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>技能Boss2</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O50" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P50" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="D51" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="n">
+        <v>2065</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K51" s="2" t="n">
-        <v>26.3</v>
+        <v>11</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>双头兽人</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P51" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -2576,42 +2540,42 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2001</v>
+        <v>2082</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>13.6</v>
+        <v>19.9</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>-0.6</v>
+        <v>4.1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>精英冬石怪</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O52" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P52" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -2619,42 +2583,42 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2008</v>
+        <v>2072</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>13.6</v>
+        <v>19.9</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>-0.6</v>
+        <v>4.1</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>精英双头兽人</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O53" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P53" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -2668,20 +2632,20 @@
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="n">
-        <v>13.6</v>
+        <v>19.9</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>-0.6</v>
+        <v>4.1</v>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -2689,42 +2653,42 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2002</v>
+        <v>2060</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>21.1</v>
+        <v>12.7</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>8.1</v>
+        <v>3.6</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>萨哈比精英坦克</t>
+          <t>蓝雪人</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O55" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P55" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -2732,69 +2696,85 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2006</v>
+        <v>2064</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>21.1</v>
+        <v>12.7</v>
       </c>
       <c r="L56" s="2" t="n">
-        <v>8.1</v>
+        <v>3.6</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>精射手</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O56" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P56" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="D57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K57" s="2" t="n">
-        <v>21.1</v>
+        <v>12.7</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>冬犀牛</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P57" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -2802,42 +2782,42 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2001</v>
+        <v>2070</v>
       </c>
       <c r="F58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="G58" s="2" t="n">
-        <v>1</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>11.4</v>
+        <v>15.4</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>-1.5</v>
+        <v>4.3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>精英绿龟</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P58" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -2845,42 +2825,42 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2008</v>
+        <v>2085</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>11.4</v>
+        <v>15.4</v>
       </c>
       <c r="L59" s="2" t="n">
-        <v>-1.5</v>
+        <v>4.3</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>影流之主</t>
+          <t>精英冬犀牛</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P59" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -2894,20 +2874,20 @@
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="n">
-        <v>11.4</v>
+        <v>15.4</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>-1.5</v>
+        <v>4.3</v>
       </c>
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr"/>
       <c r="P60" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -2915,42 +2895,42 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2001</v>
+        <v>2066</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>5.1</v>
+        <v>19.1</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>0</v>
+        <v>-4.6</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O61" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P61" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -2958,85 +2938,69 @@
         <v>19</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2003</v>
+        <v>2060</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J62" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="J62" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="K62" s="2" t="n">
-        <v>5.1</v>
+        <v>19.1</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>-4.6</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>蓝雪人</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O62" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P62" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="D63" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>2004</v>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G63" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J63" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="n">
-        <v>5.1</v>
+        <v>19.1</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>残酷射手</t>
-        </is>
-      </c>
+        <v>-4.6</v>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="n">
-        <v>3.7</v>
-      </c>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr"/>
       <c r="P63" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
@@ -3044,30 +3008,30 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2001</v>
+        <v>2074</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>-2.7</v>
+        <v>-0.9</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>普通坦克</t>
+          <t>冬蝾螈</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3076,10 +3040,10 @@
         </is>
       </c>
       <c r="O64" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P64" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -3087,30 +3051,30 @@
         <v>20</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2003</v>
+        <v>2064</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>-2.7</v>
+        <v>-0.9</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>泰森</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3119,53 +3083,37 @@
         </is>
       </c>
       <c r="O65" s="2" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="P65" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="D66" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>2008</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>影流之主</t>
-        </is>
-      </c>
+        <v>-0.9</v>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O66" s="2" t="n">
-        <v>3.7</v>
-      </c>
+      <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/新数据生成/关卡表/10050.xlsx
+++ b/新数据生成/关卡表/10050.xlsx
@@ -713,30 +713,30 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>21.5</v>
+        <v>15.6</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>-9.9</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>红蘑菇</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -755,41 +755,23 @@
       <c r="D8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>2066</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="n">
         <v>-9.9</v>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>角蜗牛</t>
-        </is>
-      </c>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="n">
         <v>4</v>
       </c>
@@ -798,41 +780,23 @@
       <c r="D9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>2079</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="n">
         <v>-9.9</v>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>冬犀牛</t>
-        </is>
-      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O9" s="2" t="inlineStr"/>
       <c r="P9" s="2" t="n">
         <v>4</v>
       </c>
@@ -842,7 +806,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>2</v>
@@ -852,20 +816,20 @@
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>20</v>
+        <v>15.8</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>精英冬龟</t>
+          <t>精英冬石怪</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -885,30 +849,28 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2081</v>
+        <v>2071</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>6</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>20</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>精英冬雪人</t>
+          <t>精英红蘑菇</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -927,25 +889,39 @@
       <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="n">
+        <v>2080</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="n">
-        <v>20</v>
-      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+        <v>3.4</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>精英冬蝾螈</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P12" s="2" t="n">
         <v>4</v>
       </c>
@@ -955,30 +931,30 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>8.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.1</v>
+        <v>-4.7</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>双头兽人</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -997,41 +973,23 @@
       <c r="D14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>2066</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>5</v>
-      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>角蜗牛</t>
-        </is>
-      </c>
+        <v>-4.7</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O14" s="2" t="inlineStr"/>
       <c r="P14" s="2" t="n">
         <v>4</v>
       </c>
@@ -1040,41 +998,23 @@
       <c r="D15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>2064</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>8.1</v>
-      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>红蘑菇</t>
-        </is>
-      </c>
+        <v>-4.7</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O15" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="n">
         <v>4</v>
       </c>
@@ -1084,35 +1024,35 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2082</v>
+        <v>2066</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>21.2</v>
+        <v>30.3</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3.8</v>
+        <v>-7.1</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>精英冬石怪</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
@@ -1126,41 +1066,23 @@
       <c r="D17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>21.2</v>
-      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>精英冬雪人</t>
-        </is>
-      </c>
+        <v>-7.1</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>轻松</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
       <c r="P17" s="2" t="n">
         <v>4</v>
       </c>
@@ -1175,16 +1097,14 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
       <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="2" t="n">
-        <v>21.2</v>
-      </c>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="n">
-        <v>3.8</v>
+        <v>-7.1</v>
       </c>
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr"/>
@@ -1197,13 +1117,13 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2062</v>
+        <v>2077</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
@@ -1213,14 +1133,14 @@
         <v>1.1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>26.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-7.3</v>
+        <v>-8.6</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>冬龟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1239,35 +1159,29 @@
       <c r="D20" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3904</t>
-        </is>
+      <c r="E20" s="2" t="n">
+        <v>2066</v>
       </c>
       <c r="F20" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>9450</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="n">
-        <v>-7.3</v>
+        <v>-8.6</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>诅咒恶鬼</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1286,25 +1200,43 @@
       <c r="D21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="n">
-        <v>26.9</v>
-      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3904</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>9450</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+        <v>-8.6</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>诅咒恶鬼</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P21" s="2" t="n">
         <v>4</v>
       </c>
@@ -1314,30 +1246,30 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>-0.9</v>
+        <v>-1.5</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>冬犀牛</t>
+          <t>冬龟</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1357,10 +1289,10 @@
         <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2074</v>
+        <v>2066</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>7</v>
@@ -1372,15 +1304,13 @@
       <c r="J23" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="K23" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="n">
-        <v>-0.9</v>
+        <v>-1.5</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>冬蝾螈</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -1399,41 +1329,23 @@
       <c r="D24" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>2064</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J24" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K24" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>红蘑菇</t>
-        </is>
-      </c>
+        <v>-1.5</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O24" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O24" s="2" t="inlineStr"/>
       <c r="P24" s="2" t="n">
         <v>4</v>
       </c>
@@ -1443,13 +1355,13 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2070</v>
+        <v>2082</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
@@ -1459,14 +1371,14 @@
         <v>1.1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>13.5</v>
+        <v>19.8</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>精英绿龟</t>
+          <t>精英冬石怪</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -1486,30 +1398,28 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2085</v>
+        <v>2080</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K26" s="2" t="n">
-        <v>13.5</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>精英冬犀牛</t>
+          <t>精英冬蝾螈</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -1528,41 +1438,23 @@
       <c r="D27" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>2072</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="2" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>精英双头兽人</t>
-        </is>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O27" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O27" s="2" t="inlineStr"/>
       <c r="P27" s="2" t="n">
         <v>4</v>
       </c>
@@ -1572,10 +1464,10 @@
         <v>8</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2060</v>
+        <v>2066</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>7</v>
@@ -1585,17 +1477,17 @@
         <v>0.6</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>21.2</v>
+        <v>19</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>-5</v>
+        <v>-6.6</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>蓝雪人</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -1614,41 +1506,23 @@
       <c r="D29" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>2064</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K29" s="2" t="n">
-        <v>21.2</v>
-      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>红蘑菇</t>
-        </is>
-      </c>
+        <v>-6.6</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O29" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="n">
         <v>4</v>
       </c>
@@ -1657,41 +1531,23 @@
       <c r="D30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>2075</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>21.2</v>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="n">
-        <v>-5</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>冬雪人</t>
-        </is>
-      </c>
+        <v>-6.6</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O30" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="n">
         <v>4</v>
       </c>
@@ -1707,20 +1563,20 @@
         <v>2</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>11.8</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>-4.5</v>
+        <v>3.9</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
@@ -1744,13 +1600,13 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
@@ -1759,15 +1615,13 @@
       <c r="J32" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K32" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="n">
-        <v>-4.5</v>
+        <v>3.9</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>红蘑菇</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -1792,11 +1646,9 @@
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="2" t="n">
-        <v>9.800000000000001</v>
-      </c>
+      <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="n">
-        <v>-4.5</v>
+        <v>3.9</v>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
@@ -1814,30 +1666,30 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2063</v>
+        <v>2077</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>16.4</v>
+        <v>14.5</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>4.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>绿龟</t>
+          <t>冬龟</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -1857,30 +1709,28 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2079</v>
+        <v>2066</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K35" s="2" t="n">
-        <v>16.4</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="n">
-        <v>4.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>冬犀牛</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -1899,41 +1749,23 @@
       <c r="D36" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>2064</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr"/>
-      <c r="I36" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J36" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K36" s="2" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>红蘑菇</t>
-        </is>
-      </c>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>地狱</t>
         </is>
       </c>
-      <c r="O36" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O36" s="2" t="inlineStr"/>
       <c r="P36" s="2" t="n">
         <v>4</v>
       </c>
@@ -1943,35 +1775,35 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>20.8</v>
+        <v>12.5</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>-7.1</v>
+        <v>-2.2</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>冬蝾螈</t>
+          <t>冬龟</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O37" s="2" t="n">
@@ -1986,35 +1818,33 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>9</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" s="2" t="n">
-        <v>20.8</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="n">
-        <v>-7.1</v>
+        <v>-2.2</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>红蘑菇</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O38" s="2" t="n">
@@ -2034,16 +1864,14 @@
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="n">
-        <v>20.8</v>
-      </c>
+      <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="n">
-        <v>-7.1</v>
+        <v>-2.2</v>
       </c>
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr"/>
@@ -2056,35 +1884,35 @@
         <v>12</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2061</v>
+        <v>2069</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>6.2</v>
+        <v>21.5</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>-1.7</v>
+        <v>2.7</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>蓝胖子</t>
+          <t>精英蓝兔子</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O40" s="2" t="n">
@@ -2099,35 +1927,33 @@
         <v>12</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2079</v>
+        <v>2071</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>9</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1.2</v>
       </c>
-      <c r="K41" s="2" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="n">
-        <v>-1.7</v>
+        <v>2.7</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>冬犀牛</t>
+          <t>精英红蘑菇</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O41" s="2" t="n">
@@ -2141,41 +1967,23 @@
       <c r="D42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>2065</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K42" s="2" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>双头兽人</t>
-        </is>
-      </c>
+        <v>2.7</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="n">
         <v>4</v>
       </c>
@@ -2185,30 +1993,30 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2079</v>
+        <v>2066</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>29.4</v>
+        <v>23.4</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-4.8</v>
+        <v>-7</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>冬犀牛</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -2227,41 +2035,23 @@
       <c r="D44" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>2060</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G44" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>29.4</v>
-      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>蓝雪人</t>
-        </is>
-      </c>
+        <v>-7</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O44" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O44" s="2" t="inlineStr"/>
       <c r="P44" s="2" t="n">
         <v>4</v>
       </c>
@@ -2276,11 +2066,9 @@
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="2" t="n">
-        <v>29.4</v>
-      </c>
+      <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="n">
-        <v>-4.8</v>
+        <v>-7</v>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
@@ -2298,13 +2086,13 @@
         <v>14</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2069</v>
+        <v>2082</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
@@ -2314,14 +2102,14 @@
         <v>1.1</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>20.6</v>
+        <v>21.3</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>3.4</v>
+        <v>8.1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>精英蓝兔子</t>
+          <t>精英冬石怪</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -2341,30 +2129,28 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2085</v>
+        <v>2080</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K47" s="2" t="n">
-        <v>20.6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="n">
-        <v>3.4</v>
+        <v>8.1</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>精英冬犀牛</t>
+          <t>精英冬蝾螈</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -2383,25 +2169,39 @@
       <c r="D48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="n">
+        <v>2071</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>11</v>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="I48" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+        <v>8.1</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>精英红蘑菇</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P48" s="2" t="n">
         <v>4</v>
       </c>
@@ -2411,30 +2211,30 @@
         <v>15</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2062</v>
+        <v>2066</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>-1</v>
+        <v>0.8</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -2453,41 +2253,23 @@
       <c r="D50" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>2066</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G50" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>角蜗牛</t>
-        </is>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O50" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O50" s="2" t="inlineStr"/>
       <c r="P50" s="2" t="n">
         <v>4</v>
       </c>
@@ -2496,41 +2278,23 @@
       <c r="D51" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E51" s="2" t="n">
-        <v>2065</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K51" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>双头兽人</t>
-        </is>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O51" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="n">
         <v>4</v>
       </c>
@@ -2540,30 +2304,30 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2082</v>
+        <v>2069</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>19.9</v>
+        <v>22.4</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>精英冬石怪</t>
+          <t>精英蓝兔子</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -2583,30 +2347,28 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2072</v>
+        <v>2080</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J53" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K53" s="2" t="n">
-        <v>19.9</v>
-      </c>
+      <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>精英双头兽人</t>
+          <t>精英冬蝾螈</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -2631,11 +2393,9 @@
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="2" t="n">
-        <v>19.9</v>
-      </c>
+      <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
@@ -2653,30 +2413,30 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2060</v>
+        <v>2077</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>12.7</v>
+        <v>9.5</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>蓝雪人</t>
+          <t>冬龟</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -2696,30 +2456,28 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="K56" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>红蘑菇</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -2738,41 +2496,23 @@
       <c r="D57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>2079</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>12.7</v>
-      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>冬犀牛</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O57" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O57" s="2" t="inlineStr"/>
       <c r="P57" s="2" t="n">
         <v>4</v>
       </c>
@@ -2782,30 +2522,30 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2070</v>
+        <v>2082</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>15.4</v>
+        <v>18.5</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>精英绿龟</t>
+          <t>精英冬石怪</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -2825,30 +2565,28 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2085</v>
+        <v>2080</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>11</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K59" s="2" t="n">
-        <v>15.4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>精英冬犀牛</t>
+          <t>精英冬蝾螈</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -2867,25 +2605,39 @@
       <c r="D60" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="n">
+        <v>2071</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>11</v>
+      </c>
       <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="2" t="n">
-        <v>15.4</v>
-      </c>
+      <c r="I60" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>精英红蘑菇</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P60" s="2" t="n">
         <v>4</v>
       </c>
@@ -2898,23 +2650,23 @@
         <v>2066</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>19.1</v>
+        <v>15.8</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>-4.6</v>
+        <v>-0.6</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2675,7 @@
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O61" s="2" t="n">
@@ -2937,41 +2689,23 @@
       <c r="D62" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="E62" s="2" t="n">
-        <v>2060</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J62" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K62" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="n">
-        <v>-4.6</v>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>蓝雪人</t>
-        </is>
-      </c>
+        <v>-0.6</v>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="n">
         <v>4</v>
       </c>
@@ -2986,16 +2720,14 @@
       <c r="H63" s="2" t="inlineStr"/>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="2" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="n">
-        <v>-4.6</v>
+        <v>-0.6</v>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr"/>
@@ -3008,30 +2740,30 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>-0.9</v>
+        <v>0.9</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>冬蝾螈</t>
+          <t>冬龟</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -3051,30 +2783,28 @@
         <v>20</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="n">
-        <v>-0.9</v>
+        <v>0.9</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>红蘑菇</t>
+          <t>角蜗牛</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -3099,11 +2829,9 @@
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
-      <c r="K66" s="2" t="n">
-        <v>9.699999999999999</v>
-      </c>
+      <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="n">
-        <v>-0.9</v>
+        <v>0.9</v>
       </c>
       <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">

--- a/新数据生成/关卡表/10050.xlsx
+++ b/新数据生成/关卡表/10050.xlsx
@@ -713,30 +713,30 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>15.6</v>
+        <v>31.6</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-9.9</v>
+        <v>-5.6</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -755,23 +755,39 @@
       <c r="D8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+        <v>-5.6</v>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>冬犀牛</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P8" s="2" t="n">
         <v>4</v>
       </c>
@@ -788,7 +804,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="n">
-        <v>-9.9</v>
+        <v>-5.6</v>
       </c>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
@@ -806,35 +822,35 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2082</v>
+        <v>2062</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>15.8</v>
+        <v>24.8</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>精英冬石怪</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O10" s="2" t="n">
@@ -849,33 +865,33 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2071</v>
+        <v>2075</v>
       </c>
       <c r="F11" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G11" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>6</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J11" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>1.1</v>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>精英红蘑菇</t>
+          <t>冬雪人</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O11" s="2" t="n">
@@ -889,39 +905,23 @@
       <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>2080</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>6</v>
-      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>精英冬蝾螈</t>
-        </is>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
       <c r="P12" s="2" t="n">
         <v>4</v>
       </c>
@@ -931,35 +931,35 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2066</v>
+        <v>2083</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>24.1</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>-4.7</v>
+        <v>3.4</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>精英冬龟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
@@ -973,23 +973,39 @@
       <c r="D14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="n">
+        <v>2071</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+        <v>3.4</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>精英红蘑菇</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr"/>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P14" s="2" t="n">
         <v>4</v>
       </c>
@@ -998,23 +1014,39 @@
       <c r="D15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+        <v>3.4</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>精英双头兽人</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr"/>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P15" s="2" t="n">
         <v>4</v>
       </c>
@@ -1024,35 +1056,35 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>30.3</v>
+        <v>20.3</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-7.1</v>
+        <v>-0.6</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
@@ -1066,23 +1098,39 @@
       <c r="D17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
-      <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+        <v>-0.6</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>冬雪人</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P17" s="2" t="n">
         <v>4</v>
       </c>
@@ -1091,23 +1139,39 @@
       <c r="D18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
-      <c r="J18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="n">
-        <v>-7.1</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+        <v>-0.6</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>冬犀牛</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P18" s="2" t="n">
         <v>4</v>
       </c>
@@ -1117,35 +1181,35 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2077</v>
+        <v>2062</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>-8.6</v>
+        <v>10.7</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>冬龟</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O19" s="2" t="n">
@@ -1160,33 +1224,33 @@
         <v>5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2066</v>
+        <v>2079</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="n">
-        <v>-8.6</v>
+        <v>10.7</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>冬犀牛</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O20" s="2" t="n">
@@ -1200,38 +1264,34 @@
       <c r="D21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>3904</t>
-        </is>
+      <c r="E21" s="2" t="n">
+        <v>2064</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>9450</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="n">
-        <v>-8.6</v>
+        <v>10.7</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>诅咒恶鬼</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O21" s="2" t="n">
@@ -1246,30 +1306,30 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2077</v>
+        <v>2062</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>12.4</v>
+        <v>25.6</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>-1.5</v>
+        <v>-4.8</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>冬龟</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -1289,28 +1349,28 @@
         <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2066</v>
+        <v>2079</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>7</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J23" s="2" t="n">
         <v>1.1</v>
-      </c>
-      <c r="J23" s="2" t="n">
-        <v>1.2</v>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="n">
-        <v>-1.5</v>
+        <v>-4.8</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>冬犀牛</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -1337,7 +1397,7 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="n">
-        <v>-1.5</v>
+        <v>-4.8</v>
       </c>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
@@ -1355,35 +1415,35 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2082</v>
+        <v>2062</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>19.8</v>
+        <v>30.8</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>3.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>精英冬石怪</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O25" s="2" t="n">
@@ -1398,33 +1458,33 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="F26" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G26" s="2" t="n">
         <v>7</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>9</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J26" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>1.1</v>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="n">
-        <v>3.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>精英冬蝾螈</t>
+          <t>冬犀牛</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O26" s="2" t="n">
@@ -1446,12 +1506,12 @@
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="n">
-        <v>3.9</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr"/>
@@ -1464,35 +1524,35 @@
         <v>8</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2066</v>
+        <v>2083</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>19</v>
+        <v>24.5</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>-6.6</v>
+        <v>6.6</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>精英冬龟</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O28" s="2" t="n">
@@ -1506,23 +1566,39 @@
       <c r="D29" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+        <v>6.6</v>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>精英双头兽人</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr"/>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P29" s="2" t="n">
         <v>4</v>
       </c>
@@ -1531,23 +1607,39 @@
       <c r="D30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="n">
+        <v>2071</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
-      <c r="J30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="n">
-        <v>-6.6</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+        <v>6.6</v>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>精英红蘑菇</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr"/>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P30" s="2" t="n">
         <v>4</v>
       </c>
@@ -1557,35 +1649,35 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2077</v>
+        <v>2062</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>11.8</v>
+        <v>28.6</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>3.9</v>
+        <v>-9.9</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>冬龟</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O31" s="2" t="n">
@@ -1600,33 +1692,33 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="n">
-        <v>3.9</v>
+        <v>-9.9</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O32" s="2" t="n">
@@ -1648,12 +1740,12 @@
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="n">
-        <v>3.9</v>
+        <v>-9.9</v>
       </c>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>轻松</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -1666,30 +1758,30 @@
         <v>10</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2077</v>
+        <v>2062</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>冬龟</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -1709,28 +1801,28 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2066</v>
+        <v>2078</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>冬战士</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -1757,7 +1849,7 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
@@ -1775,30 +1867,30 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2077</v>
+        <v>2062</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J37" s="2" t="n">
         <v>1.1</v>
       </c>
-      <c r="J37" s="2" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K37" s="2" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>-2.2</v>
+        <v>-4.4</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>冬龟</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -1818,28 +1910,28 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J38" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="J38" s="2" t="n">
-        <v>1.2</v>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="n">
-        <v>-2.2</v>
+        <v>-4.4</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -1858,23 +1950,39 @@
       <c r="D39" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="n">
+        <v>2075</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+        <v>-4.4</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>冬雪人</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P39" s="2" t="n">
         <v>4</v>
       </c>
@@ -1884,35 +1992,35 @@
         <v>12</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2069</v>
+        <v>2062</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>21.5</v>
+        <v>20.7</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>2.7</v>
+        <v>-3.8</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>精英蓝兔子</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O40" s="2" t="n">
@@ -1927,33 +2035,33 @@
         <v>12</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2071</v>
+        <v>2079</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="n">
-        <v>2.7</v>
+        <v>-3.8</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>精英红蘑菇</t>
+          <t>冬犀牛</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O41" s="2" t="n">
@@ -1967,23 +2075,39 @@
       <c r="D42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="n">
+        <v>2064</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="inlineStr"/>
-      <c r="J42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+        <v>-3.8</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>红蘑菇</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr"/>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P42" s="2" t="n">
         <v>4</v>
       </c>
@@ -1993,35 +2117,35 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2066</v>
+        <v>2083</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>23.4</v>
+        <v>18.1</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>-7</v>
+        <v>4.8</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>精英冬龟</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O43" s="2" t="n">
@@ -2035,23 +2159,39 @@
       <c r="D44" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="n">
+        <v>2085</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="n">
-        <v>-7</v>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+        <v>4.8</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>精英冬犀牛</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr"/>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P44" s="2" t="n">
         <v>4</v>
       </c>
@@ -2068,12 +2208,12 @@
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="n">
-        <v>-7</v>
+        <v>4.8</v>
       </c>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr"/>
@@ -2086,35 +2226,35 @@
         <v>14</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2082</v>
+        <v>2062</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>8.1</v>
+        <v>-3.6</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>精英冬石怪</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O46" s="2" t="n">
@@ -2129,33 +2269,33 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2080</v>
+        <v>2064</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="n">
-        <v>8.1</v>
+        <v>-3.6</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>精英冬蝾螈</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O47" s="2" t="n">
@@ -2169,39 +2309,23 @@
       <c r="D48" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>2071</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G48" s="2" t="n">
-        <v>11</v>
-      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J48" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>精英红蘑菇</t>
-        </is>
-      </c>
+        <v>-3.6</v>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr"/>
       <c r="P48" s="2" t="n">
         <v>4</v>
       </c>
@@ -2211,35 +2335,35 @@
         <v>15</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2066</v>
+        <v>2062</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>10.4</v>
+        <v>22.4</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0.8</v>
+        <v>-9.9</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>蓝兔子</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O49" s="2" t="n">
@@ -2253,23 +2377,39 @@
       <c r="D50" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="n">
+        <v>2078</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+        <v>-9.9</v>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>冬战士</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr"/>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P50" s="2" t="n">
         <v>4</v>
       </c>
@@ -2278,23 +2418,43 @@
       <c r="D51" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>12672</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>1.2</v>
+      </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+        <v>-9.9</v>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>龟仙人</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr"/>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P51" s="2" t="n">
         <v>4</v>
       </c>
@@ -2304,30 +2464,30 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2069</v>
+        <v>2083</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>22.4</v>
+        <v>18.2</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>精英蓝兔子</t>
+          <t>精英冬龟</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -2347,28 +2507,28 @@
         <v>16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2080</v>
+        <v>2072</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>精英冬蝾螈</t>
+          <t>精英双头兽人</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -2387,23 +2547,39 @@
       <c r="D54" s="2" t="n">
         <v>16</v>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="n">
+        <v>2071</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>精英红蘑菇</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P54" s="2" t="n">
         <v>4</v>
       </c>
@@ -2413,35 +2589,35 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2077</v>
+        <v>2083</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>9.5</v>
+        <v>20.8</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>冬龟</t>
+          <t>精英冬龟</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O55" s="2" t="n">
@@ -2456,33 +2632,33 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2066</v>
+        <v>2085</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>精英冬犀牛</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O56" s="2" t="n">
@@ -2496,23 +2672,39 @@
       <c r="D57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="n">
+        <v>2071</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+        <v>6.1</v>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>精英红蘑菇</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr"/>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P57" s="2" t="n">
         <v>4</v>
       </c>
@@ -2522,30 +2714,30 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>18.5</v>
+        <v>21.1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>6.4</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>精英冬石怪</t>
+          <t>精英冬龟</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -2565,20 +2757,20 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2080</v>
+        <v>2071</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="n">
@@ -2586,7 +2778,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>精英冬蝾螈</t>
+          <t>精英红蘑菇</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -2606,20 +2798,20 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="n">
@@ -2627,7 +2819,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>精英红蘑菇</t>
+          <t>精英双头兽人</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -2647,35 +2839,35 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2066</v>
+        <v>2083</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>15.8</v>
+        <v>16.9</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>-0.6</v>
+        <v>6.9</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>精英冬龟</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O61" s="2" t="n">
@@ -2689,23 +2881,39 @@
       <c r="D62" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="n">
+        <v>2085</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>9</v>
+      </c>
       <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>精英冬犀牛</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr"/>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P62" s="2" t="n">
         <v>4</v>
       </c>
@@ -2722,12 +2930,12 @@
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="n">
-        <v>-0.6</v>
+        <v>6.9</v>
       </c>
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr"/>
@@ -2740,35 +2948,35 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2077</v>
+        <v>2083</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>11.7</v>
+        <v>18.7</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>冬龟</t>
+          <t>精英冬龟</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O64" s="2" t="n">
@@ -2783,33 +2991,33 @@
         <v>20</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2066</v>
+        <v>2085</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>角蜗牛</t>
+          <t>精英冬犀牛</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O65" s="2" t="n">
@@ -2823,23 +3031,39 @@
       <c r="D66" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>10</v>
+      </c>
       <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>精英双头兽人</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr"/>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P66" s="2" t="n">
         <v>4</v>
       </c>

--- a/新数据生成/关卡表/10050.xlsx
+++ b/新数据生成/关卡表/10050.xlsx
@@ -713,30 +713,30 @@
         <v>1</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>31.6</v>
+        <v>27.6</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>-5.6</v>
+        <v>-8.1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>绿龟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -755,39 +755,21 @@
       <c r="D8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>2079</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>冬犀牛</t>
-        </is>
-      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>轻松</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O8" s="2" t="inlineStr"/>
       <c r="P8" s="2" t="n">
         <v>4</v>
       </c>
@@ -803,9 +785,7 @@
       <c r="I9" s="2" t="inlineStr"/>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="n">
-        <v>-5.6</v>
-      </c>
+      <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
@@ -822,13 +802,13 @@
         <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2062</v>
+        <v>2069</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="n">
@@ -838,19 +818,19 @@
         <v>1.2</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>24.8</v>
+        <v>23.1</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>3.6</v>
+        <v>-3.7</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>精英蓝兔子</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O10" s="2" t="n">
@@ -865,33 +845,31 @@
         <v>2</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2075</v>
+        <v>2071</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>冬雪人</t>
+          <t>精英红蘑菇</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O11" s="2" t="n">
@@ -912,13 +890,11 @@
       <c r="I12" s="2" t="inlineStr"/>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="n">
-        <v>3.6</v>
-      </c>
+      <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr"/>
@@ -931,35 +907,35 @@
         <v>3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2083</v>
+        <v>2063</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>24.1</v>
+        <v>21.9</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>3.4</v>
+        <v>-5.7</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>精英冬龟</t>
+          <t>绿龟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O13" s="2" t="n">
@@ -974,33 +950,31 @@
         <v>3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2071</v>
+        <v>2064</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>精英红蘑菇</t>
+          <t>红蘑菇</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O14" s="2" t="n">
@@ -1014,39 +988,21 @@
       <c r="D15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>2072</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>精英双头兽人</t>
-        </is>
-      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
       <c r="P15" s="2" t="n">
         <v>4</v>
       </c>
@@ -1056,35 +1012,35 @@
         <v>4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2062</v>
+        <v>2069</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>20.3</v>
+        <v>21.9</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>-0.6</v>
+        <v>-3.4</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>精英蓝兔子</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O16" s="2" t="n">
@@ -1099,33 +1055,31 @@
         <v>4</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2075</v>
+        <v>2072</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="n">
-        <v>-0.6</v>
-      </c>
+      <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>冬雪人</t>
+          <t>精英双头兽人</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O17" s="2" t="n">
@@ -1139,39 +1093,21 @@
       <c r="D18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>2079</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>冬犀牛</t>
-        </is>
-      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr"/>
       <c r="P18" s="2" t="n">
         <v>4</v>
       </c>
@@ -1181,35 +1117,35 @@
         <v>5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2062</v>
+        <v>2076</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>20</v>
+        <v>21.9</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>10.7</v>
+        <v>-7.8</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>冬石怪</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O19" s="2" t="n">
@@ -1227,22 +1163,20 @@
         <v>2079</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="n">
-        <v>10.7</v>
-      </c>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
           <t>冬犀牛</t>
@@ -1250,7 +1184,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O20" s="2" t="n">
@@ -1264,39 +1198,21 @@
       <c r="D21" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>2064</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>7</v>
-      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>红蘑菇</t>
-        </is>
-      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
       <c r="P21" s="2" t="n">
         <v>4</v>
       </c>
@@ -1306,35 +1222,35 @@
         <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2062</v>
+        <v>2069</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.2</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>25.6</v>
+        <v>18.9</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>-4.8</v>
+        <v>-4</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>精英蓝兔子</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O22" s="2" t="n">
@@ -1349,33 +1265,31 @@
         <v>6</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
-      <c r="L23" s="2" t="n">
-        <v>-4.8</v>
-      </c>
+      <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>冬犀牛</t>
+          <t>精英角蜗牛</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O23" s="2" t="n">
@@ -1396,13 +1310,11 @@
       <c r="I24" s="2" t="inlineStr"/>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="n">
-        <v>-4.8</v>
-      </c>
+      <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr"/>
@@ -1415,30 +1327,30 @@
         <v>7</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2062</v>
+        <v>2076</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>30.8</v>
+        <v>22.1</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-11.6</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>冬石怪</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -1458,28 +1370,26 @@
         <v>7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2079</v>
+        <v>2075</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="n">
-        <v>-9.300000000000001</v>
-      </c>
+      <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>冬犀牛</t>
+          <t>冬雪人</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -1505,9 +1415,7 @@
       <c r="I27" s="2" t="inlineStr"/>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="n">
-        <v>-9.300000000000001</v>
-      </c>
+      <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1524,30 +1432,30 @@
         <v>8</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>2083</v>
+        <v>2069</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>24.5</v>
+        <v>27.4</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>6.6</v>
+        <v>-14.4</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>精英冬龟</t>
+          <t>精英蓝兔子</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -1566,39 +1474,21 @@
       <c r="D29" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>2072</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>精英双头兽人</t>
-        </is>
-      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O29" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O29" s="2" t="inlineStr"/>
       <c r="P29" s="2" t="n">
         <v>4</v>
       </c>
@@ -1607,39 +1497,21 @@
       <c r="D30" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>2071</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>精英红蘑菇</t>
-        </is>
-      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O30" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O30" s="2" t="inlineStr"/>
       <c r="P30" s="2" t="n">
         <v>4</v>
       </c>
@@ -1649,35 +1521,35 @@
         <v>9</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2062</v>
+        <v>2076</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>28.6</v>
+        <v>17.2</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>-9.9</v>
+        <v>-10.9</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>冬石怪</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O31" s="2" t="n">
@@ -1692,33 +1564,31 @@
         <v>9</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2064</v>
+        <v>2079</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="n">
-        <v>-9.9</v>
-      </c>
+      <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>红蘑菇</t>
+          <t>冬犀牛</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O32" s="2" t="n">
@@ -1739,13 +1609,11 @@
       <c r="I33" s="2" t="inlineStr"/>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="n">
-        <v>-9.9</v>
-      </c>
+      <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>轻松</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr"/>
@@ -1757,36 +1625,40 @@
       <c r="D34" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>2062</v>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>3906</t>
+        </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>7248</v>
+      </c>
       <c r="I34" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>18</v>
+        <v>28.4</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>9</v>
+        <v>-16.8</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>岩石巨人2</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O34" s="2" t="n">
@@ -1800,39 +1672,21 @@
       <c r="D35" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>2078</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J35" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>冬战士</t>
-        </is>
-      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
       <c r="P35" s="2" t="n">
         <v>4</v>
       </c>
@@ -1848,13 +1702,11 @@
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>地狱</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr"/>
@@ -1867,30 +1719,30 @@
         <v>11</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2062</v>
+        <v>2076</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>-4.4</v>
+        <v>-13.4</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>冬石怪</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -1910,13 +1762,13 @@
         <v>11</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2064</v>
+        <v>2075</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="n">
@@ -1926,12 +1778,10 @@
         <v>1</v>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="n">
-        <v>-4.4</v>
-      </c>
+      <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>红蘑菇</t>
+          <t>冬雪人</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -1950,39 +1800,21 @@
       <c r="D39" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>2075</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G39" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J39" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>冬雪人</t>
-        </is>
-      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="O39" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O39" s="2" t="inlineStr"/>
       <c r="P39" s="2" t="n">
         <v>4</v>
       </c>
@@ -1992,13 +1824,13 @@
         <v>12</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2062</v>
+        <v>2069</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="n">
@@ -2008,19 +1840,19 @@
         <v>1</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>20.7</v>
+        <v>15.6</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>-3.8</v>
+        <v>-13.1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>精英蓝兔子</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O40" s="2" t="n">
@@ -2035,33 +1867,31 @@
         <v>12</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2079</v>
+        <v>2071</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="n">
-        <v>-3.8</v>
-      </c>
+      <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>冬犀牛</t>
+          <t>精英红蘑菇</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O41" s="2" t="n">
@@ -2075,39 +1905,21 @@
       <c r="D42" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>2064</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G42" s="2" t="n">
-        <v>8</v>
-      </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>红蘑菇</t>
-        </is>
-      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>困难</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr"/>
       <c r="P42" s="2" t="n">
         <v>4</v>
       </c>
@@ -2117,35 +1929,35 @@
         <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2083</v>
+        <v>2063</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>18.1</v>
+        <v>15.7</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>4.8</v>
+        <v>-15.7</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>精英冬龟</t>
+          <t>绿龟</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O43" s="2" t="n">
@@ -2160,33 +1972,31 @@
         <v>13</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2085</v>
+        <v>2079</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>精英冬犀牛</t>
+          <t>冬犀牛</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O44" s="2" t="n">
@@ -2207,13 +2017,11 @@
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr"/>
@@ -2226,35 +2034,35 @@
         <v>14</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>2062</v>
+        <v>2069</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>21.2</v>
+        <v>15.7</v>
       </c>
       <c r="L46" s="2" t="n">
-        <v>-3.6</v>
+        <v>-14.9</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>精英蓝兔子</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O46" s="2" t="n">
@@ -2269,33 +2077,31 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2064</v>
+        <v>2072</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
-      <c r="L47" s="2" t="n">
-        <v>-3.6</v>
-      </c>
+      <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>红蘑菇</t>
+          <t>精英双头兽人</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O47" s="2" t="n">
@@ -2316,13 +2122,11 @@
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="n">
-        <v>-3.6</v>
-      </c>
+      <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr"/>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>一般</t>
+          <t>困难</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr"/>
@@ -2335,13 +2139,13 @@
         <v>15</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2062</v>
+        <v>2076</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="n">
@@ -2351,19 +2155,19 @@
         <v>1.1</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>22.4</v>
+        <v>17.1</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>-9.9</v>
+        <v>-18</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>蓝兔子</t>
+          <t>冬石怪</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O49" s="2" t="n">
@@ -2378,33 +2182,31 @@
         <v>15</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>1.1</v>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="n">
-        <v>-9.9</v>
-      </c>
+      <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>冬战士</t>
+          <t>冬雪人</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O50" s="2" t="n">
@@ -2418,43 +2220,21 @@
       <c r="D51" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>3901</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H51" s="2" t="n">
-        <v>12672</v>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J51" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>龟仙人</t>
-        </is>
-      </c>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr"/>
       <c r="P51" s="2" t="n">
         <v>4</v>
       </c>
@@ -2464,13 +2244,13 @@
         <v>16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2083</v>
+        <v>2069</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="n">
@@ -2480,14 +2260,14 @@
         <v>1.1</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>18.2</v>
+        <v>15.5</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>6.4</v>
+        <v>-17.8</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>精英冬龟</t>
+          <t>精英蓝兔子</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -2510,22 +2290,20 @@
         <v>2072</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="n">
-        <v>6.4</v>
-      </c>
+      <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
           <t>精英双头兽人</t>
@@ -2548,13 +2326,13 @@
         <v>16</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="n">
@@ -2564,12 +2342,10 @@
         <v>1.1</v>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="n">
-        <v>6.4</v>
-      </c>
+      <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>精英红蘑菇</t>
+          <t>精英角蜗牛</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -2589,35 +2365,35 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2083</v>
+        <v>2076</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>20.8</v>
+        <v>15.3</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>6.1</v>
+        <v>-19.1</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>精英冬龟</t>
+          <t>冬石怪</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O55" s="2" t="n">
@@ -2632,33 +2408,31 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2085</v>
+        <v>2075</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="n">
-        <v>6.1</v>
-      </c>
+      <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>精英冬犀牛</t>
+          <t>冬雪人</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>一般</t>
         </is>
       </c>
       <c r="O56" s="2" t="n">
@@ -2672,39 +2446,21 @@
       <c r="D57" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>2071</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G57" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J57" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>精英红蘑菇</t>
-        </is>
-      </c>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>一般</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr"/>
       <c r="P57" s="2" t="n">
         <v>4</v>
       </c>
@@ -2714,30 +2470,30 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2083</v>
+        <v>2069</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>21.1</v>
+        <v>16.3</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>6.4</v>
+        <v>-19.3</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>精英冬龟</t>
+          <t>精英蓝兔子</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -2760,22 +2516,20 @@
         <v>2071</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="n">
-        <v>6.4</v>
-      </c>
+      <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
           <t>精英红蘑菇</t>
@@ -2797,39 +2551,21 @@
       <c r="D60" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>2072</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>9</v>
-      </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J60" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>精英双头兽人</t>
-        </is>
-      </c>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O60" s="2" t="n">
-        <v>5.5</v>
-      </c>
+      <c r="O60" s="2" t="inlineStr"/>
       <c r="P60" s="2" t="n">
         <v>4</v>
       </c>
@@ -2839,30 +2575,30 @@
         <v>19</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2083</v>
+        <v>2069</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>16.9</v>
+        <v>15</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>6.9</v>
+        <v>-20.3</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>精英冬龟</t>
+          <t>精英蓝兔子</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -2882,28 +2618,26 @@
         <v>19</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2085</v>
+        <v>2072</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
       <c r="I62" s="2" t="n">
         <v>0.4</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
-      <c r="L62" s="2" t="n">
-        <v>6.9</v>
-      </c>
+      <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>精英冬犀牛</t>
+          <t>精英双头兽人</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -2922,23 +2656,37 @@
       <c r="D63" s="2" t="n">
         <v>19</v>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="n">
+        <v>2071</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>5</v>
+      </c>
       <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>精英红蘑菇</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>困难</t>
         </is>
       </c>
-      <c r="O63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="n">
+        <v>5.5</v>
+      </c>
       <c r="P63" s="2" t="n">
         <v>4</v>
       </c>
@@ -2948,35 +2696,37 @@
         <v>20</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2083</v>
+        <v>3073</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H64" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>7248</v>
+      </c>
       <c r="I64" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>18.7</v>
+        <v>28.5</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>6.5</v>
+        <v>-24</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>精英冬龟</t>
+          <t>精英角蜗牛</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
+          <t>地狱</t>
         </is>
       </c>
       <c r="O64" s="2" t="n">
@@ -2990,39 +2740,21 @@
       <c r="D65" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E65" s="2" t="n">
-        <v>2085</v>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G65" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J65" s="2" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
-      <c r="L65" s="2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>精英冬犀牛</t>
-        </is>
-      </c>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>地狱</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="n">
         <v>4</v>
       </c>
@@ -3031,39 +2763,21 @@
       <c r="D66" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>2072</v>
-      </c>
-      <c r="F66" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="G66" s="2" t="n">
-        <v>10</v>
-      </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J66" s="2" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
-      <c r="L66" s="2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>精英双头兽人</t>
-        </is>
-      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>困难</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="n">
-        <v>5.5</v>
-      </c>
+          <t>地狱</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr"/>
       <c r="P66" s="2" t="n">
         <v>4</v>
       </c>
